--- a/backtest_runs/20260410_193731/by_symbol/MFL/MFL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MFL/MFL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-5395.060000000004</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>94604.94</v>
@@ -679,7 +679,7 @@
         <v>-8663.599999999997</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>90332.20999999999</v>
@@ -771,7 +771,7 @@
         <v>-846.6699999999994</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>97853.78999999999</v>
@@ -863,7 +863,7 @@
         <v>-1772.099999999997</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>96790.53</v>
@@ -909,7 +909,7 @@
         <v>-1260.160000000001</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>95530.37</v>
@@ -1185,7 +1185,7 @@
         <v>-3032.259999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>101811.48</v>
@@ -1231,7 +1231,7 @@
         <v>-2047.760000000012</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>99763.71999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-4469.629999999992</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>95294.09</v>
@@ -1323,7 +1323,7 @@
         <v>-1535.820000000002</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>93758.27</v>
@@ -1415,7 +1415,7 @@
         <v>-413.4900000000017</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>95865.10000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-1831.169999999999</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>94033.92999999999</v>
